--- a/Fase 2/Evidencias Grupales/07_Sprint_Backlog_CitaJusta.xlsx
+++ b/Fase 2/Evidencias Grupales/07_Sprint_Backlog_CitaJusta.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Backlog" sheetId="1" r:id="R180923b00bed4c72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Diario" sheetId="2" r:id="R1becd5b19a2c4020"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Sprint" sheetId="3" r:id="R411ff7f00db5478b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Backlog" sheetId="1" r:id="R7ee875f922a84564"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Diario" sheetId="2" r:id="Rb1415ae17c2646ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Sprint" sheetId="3" r:id="R1f00f890d9404f6a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -362,7 +362,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="54">
+  <x:cellXfs count="104">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -505,6 +505,140 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -844,7 +978,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdced1a55ac644a19"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb285a43944a7451b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1110,7 +1244,7 @@
   <x:sheetData>
     <x:row r="1" ht="27.75" customHeight="1">
       <x:c r="A1" s="17" t="str">
-        <x:v>CITAJUSTA SPRINT BACKLOG SPRINT 6: REASIGNACIÓN Y OFERTAS</x:v>
+        <x:v>CITAJUSTA SPRINT BACKLOG SPRINT 6: REASIGNACIÓN, OFERTAS Y NOTIFICACIONES</x:v>
       </x:c>
       <x:c r="B1" s="18"/>
       <x:c r="C1" s="18"/>
@@ -1128,7 +1262,7 @@
     </x:row>
     <x:row r="2" ht="37.5" customHeight="1">
       <x:c r="A2" s="20" t="str">
-        <x:v>Versión 1.3 · 20-09-2026 · Sprint 6 con cierre técnico completado. Backend y experiencia Web de ofertas/reasignación implementados y validados; HU-022 queda lista para commit/PR/merge.</x:v>
+        <x:v>Versión 1.4 · 21-09-2026 · Sprint 6 cerrado con 10/10 tareas. HU-023 completa RF-029/RF-030 y HU-024 completa RF-034; ambas mergeadas a main.</x:v>
       </x:c>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -1169,7 +1303,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Cerrado técnicamente</x:v>
+        <x:v>Cerrado</x:v>
       </x:c>
       <x:c r="C6" s="18"/>
       <x:c r="D6" s="19"/>
@@ -1179,7 +1313,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="24" t="str">
-        <x:v>20-09-2026</x:v>
+        <x:v>21-09-2026</x:v>
       </x:c>
       <x:c r="C7" s="18"/>
       <x:c r="D7" s="19"/>
@@ -1199,7 +1333,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="25" t="str">
-        <x:v>Este Sprint Backlog concentra el motor de reasignación y su integración Web. Las ocho tareas planificadas alcanzaron Done con evidencia verificable. La integración a main de HU-022 queda como cierre administrativo posterior al corte; las horas reales no se reconstruyen retrospectivamente.</x:v>
+        <x:v>Este Sprint Backlog concentra el motor de reasignación, su experiencia Web y el cierre de requisitos MVP asociados a expiración/continuidad y notificaciones internas. Tras refinamiento del alcance, S6-T09 y S6-T10 se incorporaron para cerrar RF-029/RF-030/RF-034 antes de iniciar el bloque institucional. Las 10 tareas están Done con evidencia verificable.</x:v>
       </x:c>
       <x:c r="C9" s="21"/>
       <x:c r="D9" s="22"/>
@@ -1548,12 +1682,12 @@
         <x:v>Usuario puede ver oferta real, expiresAt, aceptar/rechazar y observar estado final sin lógica crítica en cliente</x:v>
       </x:c>
       <x:c r="K19" s="3" t="str">
-        <x:v>feat/web-reassignment-offers</x:v>
+        <x:v>feat/web-reassignment-offers · PR #93 · merge 5701ab7</x:v>
       </x:c>
       <x:c r="L19" s="3"/>
       <x:c r="M19" s="3"/>
       <x:c r="N19" s="3" t="str">
-        <x:v>Web /ofertas implementada con GET propio, expiresAt real, aceptación/rechazo y estados finales. Web 71/71; pruebas enfocadas 10/10; E2E reasignaciones 20/20; prueba manual ACCEPT/REJECT/expiración PASS.</x:v>
+        <x:v>Web /ofertas validada con ACCEPT/REJECT/expiración visual. Mergeada a main mediante PR #93.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="85.5" customHeight="1">
@@ -1586,16 +1720,90 @@
         <x:v>Flujo integrado validado con contratos reales, concurrencia y errores controlados</x:v>
       </x:c>
       <x:c r="K20" s="15" t="str">
-        <x:v>feat/web-reassignment-offers</x:v>
+        <x:v>feat/web-reassignment-offers · PR #93</x:v>
       </x:c>
       <x:c r="L20" s="15"/>
       <x:c r="M20" s="15"/>
       <x:c r="N20" s="15" t="str">
-        <x:v>Validación final completada contra Web + API + PostgreSQL: oferta vencida sin mutación, ACCEPT transfiere la cita existente y REJECT no crea cita. Build API/Web, Prisma validate, check:dev y git diff --check PASS.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="15.75" customHeight="1"/>
-    <x:row r="22" ht="15.75" customHeight="1"/>
+        <x:v>Validación Web + API + PostgreSQL completada; ACCEPT transfiere cita existente y REJECT no crea cita.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="58" customHeight="1">
+      <x:c r="A21" s="67" t="str">
+        <x:v>HU-023</x:v>
+      </x:c>
+      <x:c r="B21" s="67" t="str">
+        <x:v>S6-T09</x:v>
+      </x:c>
+      <x:c r="C21" s="67" t="str">
+        <x:v>Automatizar expiración de ofertas y continuidad de reasignación</x:v>
+      </x:c>
+      <x:c r="D21" s="67" t="str">
+        <x:v>Backend / Runner</x:v>
+      </x:c>
+      <x:c r="E21" s="67" t="str">
+        <x:v>Crítica</x:v>
+      </x:c>
+      <x:c r="F21" s="67"/>
+      <x:c r="G21" s="67" t="str">
+        <x:v>Equipo CitaJusta</x:v>
+      </x:c>
+      <x:c r="H21" s="67" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I21" s="67" t="str">
+        <x:v>HU-009/010/011 + HU-018</x:v>
+      </x:c>
+      <x:c r="J21" s="67" t="str">
+        <x:v>Oferta vencida pasa a EXPIRED; continuidad idempotente genera siguiente oferta o cierra EXHAUSTED/CANCELLED de forma segura</x:v>
+      </x:c>
+      <x:c r="K21" s="67" t="str">
+        <x:v>feat/automatic-offer-expiration · PR #96 · merge 109b1c9</x:v>
+      </x:c>
+      <x:c r="L21" s="67"/>
+      <x:c r="M21" s="67"/>
+      <x:c r="N21" s="67" t="str">
+        <x:v>API 368/368; E2E expiry 10/10; reasignaciones 20/20; audit 11/11; policy 13/13; reports 15/15; checkpoint 1/1.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="58" customHeight="1">
+      <x:c r="A22" s="67" t="str">
+        <x:v>HU-024</x:v>
+      </x:c>
+      <x:c r="B22" s="67" t="str">
+        <x:v>S6-T10</x:v>
+      </x:c>
+      <x:c r="C22" s="67" t="str">
+        <x:v>Implementar notificaciones internas</x:v>
+      </x:c>
+      <x:c r="D22" s="67" t="str">
+        <x:v>Backend / Web</x:v>
+      </x:c>
+      <x:c r="E22" s="67" t="str">
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="F22" s="67"/>
+      <x:c r="G22" s="67" t="str">
+        <x:v>Equipo CitaJusta</x:v>
+      </x:c>
+      <x:c r="H22" s="67" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I22" s="67" t="str">
+        <x:v>HU-004/006/007/008/009/010/011/023</x:v>
+      </x:c>
+      <x:c r="J22" s="67" t="str">
+        <x:v>Ocho eventos generan notificaciones deduplicadas; usuario consulta sólo las propias, marca lectura y Web muestra contador/listado persistente</x:v>
+      </x:c>
+      <x:c r="K22" s="67" t="str">
+        <x:v>feat/internal-notifications · PR #99 · merge b1bff30</x:v>
+      </x:c>
+      <x:c r="L22" s="67"/>
+      <x:c r="M22" s="67"/>
+      <x:c r="N22" s="67" t="str">
+        <x:v>API nuevos 6/6; E2E notifications 8/8; API dirigida 157/157; regresión crítica 87/87; Web 83/83; prueba manual lectura + logout/login PASS.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" ht="15.75" customHeight="1"/>
     <x:row r="24" ht="15.75" customHeight="1"/>
     <x:row r="25" ht="15.75" customHeight="1"/>
@@ -2616,7 +2824,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R407398c9befa439d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14387af5ced7420a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2656,7 +2864,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="27" t="str">
-        <x:v>No se reconstruyen horas históricas. S6-T01 a S6-T08 están completadas técnicamente con evidencia verificable. Registrar consumo horario sólo cuando exista evidencia real.</x:v>
+        <x:v>No se reconstruyen horas históricas. S6-T01 a S6-T10 están completadas con evidencia verificable. S6-T09/S6-T10 cierran los requisitos MVP de expiración/continuidad y notificaciones internas.</x:v>
       </x:c>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -3010,6 +3218,50 @@
       </x:c>
       <x:c r="P13" s="6" t="str">
         <x:v>Validación integrada completada con escenarios reales de expiración, aceptación y rechazo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="38" customHeight="1">
+      <x:c r="A14" s="67"/>
+      <x:c r="B14" s="67" t="str">
+        <x:v>S6-T09</x:v>
+      </x:c>
+      <x:c r="C14" s="67" t="str"/>
+      <x:c r="D14" s="67" t="str"/>
+      <x:c r="E14" s="67" t="str"/>
+      <x:c r="F14" s="67" t="str"/>
+      <x:c r="G14" s="67" t="str"/>
+      <x:c r="H14" s="67" t="str"/>
+      <x:c r="I14" s="67" t="str"/>
+      <x:c r="J14" s="67" t="str"/>
+      <x:c r="K14" s="67" t="str"/>
+      <x:c r="L14" s="67" t="str"/>
+      <x:c r="M14" s="67" t="str"/>
+      <x:c r="N14" s="67" t="str"/>
+      <x:c r="O14" s="67" t="str"/>
+      <x:c r="P14" s="67" t="str">
+        <x:v>HU-023 completada y mergeada. Horas diarias no reconstruidas retrospectivamente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="38" customHeight="1">
+      <x:c r="A15" s="67"/>
+      <x:c r="B15" s="67" t="str">
+        <x:v>S6-T10</x:v>
+      </x:c>
+      <x:c r="C15" s="67" t="str"/>
+      <x:c r="D15" s="67" t="str"/>
+      <x:c r="E15" s="67" t="str"/>
+      <x:c r="F15" s="67" t="str"/>
+      <x:c r="G15" s="67" t="str"/>
+      <x:c r="H15" s="67" t="str"/>
+      <x:c r="I15" s="67" t="str"/>
+      <x:c r="J15" s="67" t="str"/>
+      <x:c r="K15" s="67" t="str"/>
+      <x:c r="L15" s="67" t="str"/>
+      <x:c r="M15" s="67" t="str"/>
+      <x:c r="N15" s="67" t="str"/>
+      <x:c r="O15" s="67" t="str"/>
+      <x:c r="P15" s="67" t="str">
+        <x:v>HU-024 completada y mergeada. Prueba manual de centro de notificaciones y persistencia de lectura PASS.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -4004,7 +4256,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re81824a0ffbe4d3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R136a8eda2e2f4e7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4023,7 +4275,7 @@
   <x:sheetData>
     <x:row r="1" ht="20.25">
       <x:c r="A1" s="28" t="str">
-        <x:v>CITAJUSTA — RESUMEN SPRINT 6: REASIGNACIÓN Y OFERTAS — CIERRE TÉCNICO</x:v>
+        <x:v>CITAJUSTA — RESUMEN SPRINT 6: REASIGNACIÓN, OFERTAS Y NOTIFICACIONES — CERRADO</x:v>
       </x:c>
       <x:c r="B1" s="29"/>
       <x:c r="C1" s="29"/>
@@ -4049,14 +4301,14 @@
         <x:v>Tareas planificadas</x:v>
       </x:c>
       <x:c r="B4" s="10" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:f t="shared" ref="E4:E6" si="0">B6</x:f>
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4079,7 +4331,7 @@
         <x:v>Tareas Done</x:v>
       </x:c>
       <x:c r="B6" s="10" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>Pendiente</x:v>
@@ -4130,7 +4382,7 @@
         <x:v>Validación actual</x:v>
       </x:c>
       <x:c r="B10" s="13" t="str">
-        <x:v>Web 71/71 · recipient/demo 10/10 · E2E reasignaciones 20/20</x:v>
+        <x:v>HU-023: API 368/368 + expiry 10/10 · HU-024: Web 83/83 + notifications 8/8</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="71.25">
@@ -4138,7 +4390,7 @@
         <x:v>Pruebas actuales</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>Web 71/71 · recipient/demo 10/10 · E2E reasignaciones 20/20 · API/Web build · Prisma/check:dev OK</x:v>
+        <x:v>HU-023 y HU-024 con unitarios/E2E/regresión dirigida, builds, Prisma y pruebas manuales PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4154,19 +4406,19 @@
     <x:row r="15">
       <x:c r="A15" s="32" t="str">
         <x:v>• HU-009/010/011/016/018 backend completadas.
-• HU-021 Web de lista de espera/preferencias completada y mergeada por PR #89.
-• HU-022 Web de ofertas/reasignación completada técnicamente.
-• GET /reassignments/offers/me y ruta /ofertas implementados con aislamiento por destinatario.
-• seed:reassignment-demo permite escenarios accept/reject mediante dominio real.
-• Validación: Web 71/71, pruebas enfocadas 10/10 y E2E reasignaciones 20/20; prueba manual completa PASS.</x:v>
+• HU-021 Web waitlist/preferencias Done (PR #89).
+• HU-022 Web ofertas Done (PR #93).
+• HU-023 expiración automática/continuidad Done (PR #96).
+• HU-024 notificaciones internas + centro Web Done (PR #99).
+• RF-029/RF-030/RF-034 cerrados con evidencia automática y manual.</x:v>
       </x:c>
       <x:c r="B15" s="33"/>
       <x:c r="C15" s="16"/>
       <x:c r="D15" s="38" t="str">
-        <x:v>• Commit, push, PR y merge de feat/web-reassignment-offers.
-• Mover HU-022 a Done en GitHub Projects después del merge.
-• Continuar con interfaces institucionales del siguiente Sprint.
-• Mantener como deuda técnica separada la advertencia de pg en consultas concurrentes.</x:v>
+        <x:v>• Ningún pendiente técnico dentro del alcance refinado del Sprint 6.
+• Actualizar evidencias Scrum y Mapa Maestro.
+• Revisar cierre de la Web de usuario frente a alcance/bocetos.
+• Iniciar posteriormente la aplicación institucional de escritorio.</x:v>
       </x:c>
       <x:c r="E15" s="33"/>
     </x:row>
@@ -4208,7 +4460,7 @@
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="39" t="str">
-        <x:v>Evidencia técnica al 20-09-2026</x:v>
+        <x:v>Evidencia técnica al 21-09-2026</x:v>
       </x:c>
       <x:c r="B22" s="18"/>
       <x:c r="C22" s="18"/>
@@ -4217,7 +4469,7 @@
     </x:row>
     <x:row r="23" ht="72" customHeight="1">
       <x:c r="A23" s="45" t="str">
-        <x:v>Sprint 6 alcanza cierre técnico con 8/8 tareas Done. HU-022 quedó validada automática y manualmente; la rama feat/web-reassignment-offers está lista para integración administrativa a main. Las horas reales no se reconstruyen retrospectivamente.</x:v>
+        <x:v>Sprint 6 cerrado con 10/10 tareas Done. HU-023 y HU-024 están mergeadas a main mediante PR #96 y #99. La expiración automática, continuidad de ofertas y notificaciones internas ya forman parte del MVP verificable.</x:v>
       </x:c>
       <x:c r="B23" s="46"/>
       <x:c r="C23" s="46"/>
@@ -5230,6 +5482,6 @@
     <x:mergeCell ref="D15:E20"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree4b3f207e8645f9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeccc888cc0a407c"/>
 </x:worksheet>
 </file>